--- a/r4-ELGA-AustrianPatientSummary-48-30-53-71---remove-ordered-and-closed-slicing-within-composition/StructureDefinition-at-aps-flagalert.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-48-30-53-71---remove-ordered-and-closed-slicing-within-composition/StructureDefinition-at-aps-flagalert.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T10:12:59+00:00</t>
+    <t>2026-01-28T10:16:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
